--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484362_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484362_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3525</v>
+        <v>2.6364</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6335</v>
+        <v>4.8357</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.281</v>
+        <v>-2.1993</v>
       </c>
       <c r="G2" t="n">
         <v>1.9932</v>
@@ -610,13 +610,13 @@
         <v>1.5627</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3087</v>
+        <v>-0.0247</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4541</v>
+        <v>0.6564</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7628</v>
+        <v>-0.6811</v>
       </c>
       <c r="V2" t="n">
         <v>0.2772</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>M. LLUCIÀ MONSÓ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0855</v>
+        <v>2.1066</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0727</v>
+        <v>1.7404</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.9873</v>
+        <v>0.3662</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6672</v>
+        <v>1.9264</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4502</v>
+        <v>-0.2047</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1174</v>
+        <v>2.1311</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9293</v>
+        <v>1.8614</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5973000000000001</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>3.332</v>
+        <v>1.8614</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.2621</v>
+        <v>0.065</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0476</v>
+        <v>-0.2047</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2146</v>
+        <v>0.2696</v>
       </c>
       <c r="P3" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1643</v>
+        <v>-0.0151</v>
       </c>
       <c r="T3" t="n">
-        <v>1.175</v>
+        <v>-0.121</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0106</v>
+        <v>0.1059</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. LLUCIÀ MONSÓ</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0794</v>
+        <v>1.2258</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7404</v>
+        <v>3.5672</v>
       </c>
       <c r="F4" t="n">
-        <v>0.339</v>
+        <v>-2.3413</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9264</v>
+        <v>1.6672</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2047</v>
+        <v>-0.4502</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1311</v>
+        <v>2.1174</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8614</v>
+        <v>3.9293</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8614</v>
+        <v>3.332</v>
       </c>
       <c r="M4" t="n">
-        <v>0.065</v>
+        <v>-2.2621</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2047</v>
+        <v>-1.0476</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2696</v>
+        <v>-1.2146</v>
       </c>
       <c r="P4" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0424</v>
+        <v>0.3047</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.121</v>
+        <v>0.6694</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07870000000000001</v>
+        <v>-0.3647</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.9414</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.0549</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ QUILEZ</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9304</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3491</v>
+        <v>2.3209</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4186</v>
+        <v>-1.5613</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5526</v>
+        <v>1.4</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5526</v>
+        <v>-1.163</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2.563</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0614</v>
+        <v>2.8382</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0614</v>
+        <v>-0.2648</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.103</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.614</v>
+        <v>-1.4382</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.614</v>
+        <v>-0.8982</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.5401</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2877</v>
+        <v>0.2229</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2877</v>
+        <v>0.2175</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.0054</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="6">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1348</v>
+        <v>0.337</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.2022</v>
       </c>
       <c r="F6" t="n">
         <v>0.1348</v>
@@ -922,10 +922,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.2022</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.2022</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>A. FERNANDEZ QUILEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0633</v>
+        <v>0.1215</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4387</v>
+        <v>0.5402</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3754</v>
+        <v>-0.4186</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8982</v>
+        <v>-0.5526</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5337</v>
+        <v>-0.5526</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3646</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8331</v>
+        <v>0.0614</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0167</v>
+        <v>0.0614</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8498</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.7314</v>
+        <v>-0.614</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.517</v>
+        <v>-0.614</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2144</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>0.1953</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.4788</v>
       </c>
       <c r="T7" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.4788</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7030999999999999</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7182</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1052</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1582</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>1.512</v>
+        <v>2.5398</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6702</v>
+        <v>-2.6205</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4</v>
+        <v>-1.8982</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.163</v>
+        <v>-1.5337</v>
       </c>
       <c r="I8" t="n">
-        <v>2.563</v>
+        <v>-0.3646</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8382</v>
+        <v>0.8331</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2648</v>
+        <v>-0.0167</v>
       </c>
       <c r="L8" t="n">
-        <v>3.103</v>
+        <v>0.8498</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4382</v>
+        <v>-2.7314</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8982</v>
+        <v>-1.517</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5401</v>
+        <v>-1.2144</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>-0.1953</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.695</v>
+        <v>0.6418</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5915</v>
+        <v>0.1838</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1035</v>
+        <v>0.458</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2772</v>
+        <v>-0.3869</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2186</v>
+        <v>1.7182</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4959</v>
+        <v>-2.1052</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4661</v>
+        <v>-0.6603</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3749</v>
+        <v>1.8273</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8409</v>
+        <v>-2.4876</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6819</v>
+        <v>-0.2653</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5733</v>
+        <v>0.6644</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1086</v>
+        <v>-0.9297</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3062</v>
+        <v>2.0614</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6577</v>
+        <v>2.0466</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6484</v>
+        <v>0.0148</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6243</v>
+        <v>-2.3267</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0844</v>
+        <v>-1.3822</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5399</v>
+        <v>-0.9445</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9767</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9534</v>
+        <v>-3.1255</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0474</v>
+        <v>-0.1327</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8035</v>
+        <v>0.1769</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7561</v>
+        <v>-0.3096</v>
       </c>
       <c r="V9" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.7145</v>
+      </c>
+      <c r="X9" t="n">
         <v>-1.2186</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.2186</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-2.4373</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4498</v>
+        <v>-0.8821</v>
       </c>
       <c r="E10" t="n">
-        <v>1.1195</v>
+        <v>1.7682</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5693</v>
+        <v>-2.6503</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2653</v>
+        <v>1.6819</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6644</v>
+        <v>1.5733</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9297</v>
+        <v>0.1086</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0614</v>
+        <v>2.3062</v>
       </c>
       <c r="K10" t="n">
-        <v>2.0466</v>
+        <v>1.6577</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0148</v>
+        <v>0.6484</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3267</v>
+        <v>-0.6243</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3822</v>
+        <v>-0.0844</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9445</v>
+        <v>-0.5399</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7581</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1255</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9222</v>
+        <v>-0.3687</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5309</v>
+        <v>0.1968</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3913</v>
+        <v>-0.5655</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4959</v>
+        <v>-1.2186</v>
       </c>
       <c r="W10" t="n">
-        <v>2.7145</v>
+        <v>1.2186</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4707</v>
+        <v>-4.1283</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2482</v>
+        <v>-3.445</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2225</v>
+        <v>-0.6833</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.153</v>
+        <v>-2.3757</v>
       </c>
       <c r="H11" t="n">
         <v>-2.8074</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3456</v>
+        <v>0.4317</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.6259</v>
+        <v>-0.6532</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.8995</v>
+        <v>-1.4902</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7264</v>
+        <v>0.837</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5271</v>
+        <v>-1.7225</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9079</v>
+        <v>-1.3172</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.6192</v>
+        <v>-0.4052</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3907</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1488</v>
+        <v>-3.1255</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7958</v>
+        <v>-0.2717</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2493</v>
+        <v>-0.2207</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4535</v>
+        <v>-0.051</v>
       </c>
       <c r="V11" t="n">
         <v>0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>0.5545</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5521</v>
+        <v>-4.8867</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9505</v>
+        <v>-3.8549</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6016</v>
+        <v>-1.0319</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.3757</v>
+        <v>-5.153</v>
       </c>
       <c r="H12" t="n">
         <v>-2.8074</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4317</v>
+        <v>-2.3456</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6532</v>
+        <v>-2.6259</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.4902</v>
+        <v>-1.8995</v>
       </c>
       <c r="L12" t="n">
-        <v>0.837</v>
+        <v>-0.7264</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7225</v>
+        <v>-2.5271</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3172</v>
+        <v>-0.9079</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4052</v>
+        <v>-1.6192</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.7581</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.1255</v>
+        <v>-2.1488</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6956</v>
+        <v>0.3797</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7262999999999999</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0307</v>
+        <v>-0.2629</v>
       </c>
       <c r="V12" t="n">
         <v>0.2772</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5545</v>
+        <v>0.2772</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.450999999999999</v>
+        <v>-3.4512</v>
       </c>
       <c r="E13" t="n">
-        <v>12.0421</v>
+        <v>12.042</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.493</v>
+        <v>-15.4931</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.441299999999999</v>
+        <v>-1.4413</v>
       </c>
       <c r="H13" t="n">
         <v>-6.164099999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>4.7227</v>
+        <v>4.722700000000001</v>
       </c>
       <c r="J13" t="n">
         <v>15.6861</v>
@@ -1456,7 +1456,7 @@
         <v>-9.704599999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.4231</v>
+        <v>-7.423100000000001</v>
       </c>
       <c r="P13" t="n">
         <v>-2.9303</v>
@@ -1468,16 +1468,16 @@
         <v>11.7205</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4171</v>
+        <v>1.4172</v>
       </c>
       <c r="T13" t="n">
-        <v>3.0825</v>
+        <v>3.0827</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.6653</v>
+        <v>-1.6655</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.4965999999999999</v>
+        <v>-0.4965999999999997</v>
       </c>
       <c r="W13" t="n">
         <v>7.9239</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6247</v>
+        <v>3.6093</v>
       </c>
       <c r="E14" t="n">
-        <v>5.1285</v>
+        <v>3.8981</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5037</v>
+        <v>-0.2888</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2273</v>
+        <v>3.5497</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4983</v>
+        <v>1.7552</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7256</v>
+        <v>1.7945</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6851</v>
+        <v>6.0076</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1996</v>
+        <v>2.4584</v>
       </c>
       <c r="L14" t="n">
-        <v>3.8847</v>
+        <v>3.5491</v>
       </c>
       <c r="M14" t="n">
         <v>-2.4579</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2988</v>
+        <v>-0.7032</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.1591</v>
+        <v>-1.7546</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5395</v>
+        <v>2.7348</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0737</v>
+        <v>-0.4093</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4404</v>
+        <v>0.2113</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3667</v>
+        <v>-0.6206</v>
       </c>
       <c r="V14" t="n">
-        <v>2.7145</v>
+        <v>0.6642</v>
       </c>
       <c r="W14" t="n">
-        <v>3.9331</v>
+        <v>0.6093</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2186</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3951</v>
+        <v>3.5689</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2014</v>
+        <v>5.1285</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8063</v>
+        <v>-1.5596</v>
       </c>
       <c r="G15" t="n">
-        <v>3.5497</v>
+        <v>1.2273</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7552</v>
+        <v>-0.4983</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7945</v>
+        <v>1.7256</v>
       </c>
       <c r="J15" t="n">
-        <v>6.0076</v>
+        <v>3.6851</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4584</v>
+        <v>-0.1996</v>
       </c>
       <c r="L15" t="n">
-        <v>3.5491</v>
+        <v>3.8847</v>
       </c>
       <c r="M15" t="n">
         <v>-2.4579</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7032</v>
+        <v>-0.2988</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.7546</v>
+        <v>-2.1591</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7348</v>
+        <v>2.5395</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6234</v>
+        <v>0.0178</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5147</v>
+        <v>0.4404</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.138</v>
+        <v>-0.4225</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6642</v>
+        <v>2.7145</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6093</v>
+        <v>3.9331</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0549</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.893</v>
+        <v>1.6829</v>
       </c>
       <c r="E16" t="n">
-        <v>3.015</v>
+        <v>2.9138</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.122</v>
+        <v>-1.2309</v>
       </c>
       <c r="G16" t="n">
         <v>2.7216</v>
@@ -1702,13 +1702,13 @@
         <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4253</v>
+        <v>0.2153</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6357</v>
+        <v>0.5346</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2104</v>
+        <v>-0.3193</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2772</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6856</v>
+        <v>1.5456</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0915</v>
+        <v>1.7882</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4059</v>
+        <v>-0.2425</v>
       </c>
       <c r="G17" t="n">
         <v>0.0098</v>
@@ -1780,13 +1780,13 @@
         <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2851</v>
+        <v>0.1452</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4458</v>
+        <v>0.1424</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1607</v>
+        <v>0.0027</v>
       </c>
       <c r="V17" t="n">
         <v>0.6093</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.05</v>
+        <v>0.3151</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7481</v>
+        <v>4.6225</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.698</v>
+        <v>-4.3074</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.5406</v>
+        <v>0.2329</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3784</v>
+        <v>1.9322</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1623</v>
+        <v>-1.6994</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0974</v>
+        <v>2.7606</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.55</v>
+        <v>2.7053</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6475</v>
+        <v>0.0553</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.638</v>
+        <v>-2.5277</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8283</v>
+        <v>-0.7731</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8097</v>
+        <v>-1.7546</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7814</v>
+        <v>2.5395</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>2.5395</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1321</v>
+        <v>-0.2972</v>
       </c>
       <c r="T18" t="n">
-        <v>0.432</v>
+        <v>0.3661</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5641</v>
+        <v>-0.6633</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9414</v>
+        <v>-2.16</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>1.4959</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>-3.6559</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3331</v>
+        <v>-0.0861</v>
       </c>
       <c r="E19" t="n">
-        <v>4.218</v>
+        <v>1.7481</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.5511</v>
+        <v>-1.8342</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2329</v>
+        <v>-1.5406</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9322</v>
+        <v>-1.3784</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6994</v>
+        <v>-0.1623</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7606</v>
+        <v>0.0974</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7053</v>
+        <v>-0.55</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0553</v>
+        <v>0.6475</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.5277</v>
+        <v>-1.638</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7731</v>
+        <v>-0.8283</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7546</v>
+        <v>-0.8097</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5395</v>
+        <v>0.7814</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5395</v>
+        <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9454</v>
+        <v>-0.2683</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0384</v>
+        <v>0.432</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.907</v>
+        <v>-0.7003</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.16</v>
+        <v>0.9414</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4959</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.6559</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>J. CASCALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3579</v>
+        <v>-1.4328</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2099</v>
+        <v>-1.3061</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.148</v>
+        <v>-0.1267</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0082</v>
+        <v>-2.5152</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1793</v>
+        <v>0.1011</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1875</v>
+        <v>-2.6163</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2859</v>
+        <v>-1.2263</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1241</v>
+        <v>0.0409</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1619</v>
+        <v>-1.2673</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2941</v>
+        <v>-1.2889</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0553</v>
+        <v>0.0601</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3494</v>
+        <v>-1.349</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3648</v>
+        <v>-0.1678</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2037</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1611</v>
+        <v>-0.0881</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4959</v>
+        <v>0.6642</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7731</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CASCALES FERNANDEZ</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.081</v>
+        <v>-1.4331</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7105</v>
+        <v>-0.311</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3705</v>
+        <v>-1.1221</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.5152</v>
+        <v>-1.0082</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1011</v>
+        <v>0.1793</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.6163</v>
+        <v>-1.1875</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2263</v>
+        <v>0.2859</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0409</v>
+        <v>0.1241</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2673</v>
+        <v>0.1619</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2889</v>
+        <v>-1.2941</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0601</v>
+        <v>0.0553</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.349</v>
+        <v>-1.3494</v>
       </c>
       <c r="P21" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8159999999999999</v>
+        <v>0.2896</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4842</v>
+        <v>0.1026</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3318</v>
+        <v>0.187</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6642</v>
+        <v>-1.4959</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6642</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4254</v>
+        <v>-3.6446</v>
       </c>
       <c r="E22" t="n">
         <v>-2.989</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4363</v>
+        <v>-0.6556</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2358</v>
@@ -2170,13 +2170,13 @@
         <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.049</v>
+        <v>-0.2683</v>
       </c>
       <c r="T22" t="n">
         <v>-0.4842</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4351</v>
+        <v>0.2159</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1638</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.451</v>
+        <v>4.125200000000001</v>
       </c>
       <c r="E23" t="n">
         <v>15.4931</v>
       </c>
       <c r="F23" t="n">
-        <v>-12.0418</v>
+        <v>-11.3678</v>
       </c>
       <c r="G23" t="n">
         <v>1.4415</v>
@@ -2248,13 +2248,13 @@
         <v>14.6508</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.417</v>
+        <v>-0.743</v>
       </c>
       <c r="T23" t="n">
         <v>1.6655</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.0825</v>
+        <v>-2.4085</v>
       </c>
       <c r="V23" t="n">
         <v>0.4967000000000004</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484362_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484362_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,143 +563,148 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6364</v>
+        <v>2.4349</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8357</v>
+        <v>2.4349</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.1993</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9932</v>
+        <v>2.4349</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1172</v>
+        <v>0.614</v>
       </c>
       <c r="I2" t="n">
-        <v>0.876</v>
+        <v>1.821</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0742</v>
+        <v>2.4349</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8485</v>
+        <v>0.614</v>
       </c>
       <c r="L2" t="n">
-        <v>2.2256</v>
+        <v>1.821</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.081</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7314</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.3496</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0247</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6564</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6811</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. LLUCIÀ MONSÓ</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1066</v>
+        <v>2.1279</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7404</v>
+        <v>2.1279</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3662</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9264</v>
+        <v>2.1279</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2047</v>
+        <v>0.307</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1311</v>
+        <v>1.821</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8614</v>
+        <v>2.1279</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.307</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8614</v>
+        <v>1.821</v>
       </c>
       <c r="M3" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2047</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2696</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0151</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.121</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1059</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -704,306 +714,326 @@
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>M. LLUCIA MONSO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2258</v>
+        <v>2.1066</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5672</v>
+        <v>1.7404</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.3413</v>
+        <v>0.3662</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6672</v>
+        <v>1.9264</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4502</v>
+        <v>-0.2047</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1174</v>
+        <v>2.1311</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9293</v>
+        <v>1.8614</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5973000000000001</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3.332</v>
+        <v>1.8614</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2621</v>
+        <v>0.065</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0476</v>
+        <v>-0.2047</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2146</v>
+        <v>0.2696</v>
       </c>
       <c r="P4" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3047</v>
+        <v>-0.0151</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6694</v>
+        <v>-0.121</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3647</v>
+        <v>0.1059</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7596000000000001</v>
+        <v>1.2258</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3209</v>
+        <v>3.5672</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5613</v>
+        <v>-2.3413</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4</v>
+        <v>1.6672</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.163</v>
+        <v>-0.4502</v>
       </c>
       <c r="I5" t="n">
-        <v>2.563</v>
+        <v>2.1174</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8382</v>
+        <v>3.9293</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2648</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>3.103</v>
+        <v>3.332</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4382</v>
+        <v>-2.2621</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8982</v>
+        <v>-1.0476</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5401</v>
+        <v>-1.2146</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2229</v>
+        <v>0.3047</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2175</v>
+        <v>0.6694</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0054</v>
+        <v>-0.3647</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2772</v>
+        <v>-0.9414</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2186</v>
+        <v>-0.0549</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4959</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. SUÑOL CUBARSI</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.337</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2022</v>
+        <v>2.3209</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1348</v>
+        <v>-1.5613</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1348</v>
+        <v>1.4</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-1.163</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1348</v>
+        <v>2.563</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2.8382</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-0.2648</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.103</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1348</v>
+        <v>-1.4382</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.8982</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1348</v>
+        <v>-0.5401</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.586</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2022</v>
+        <v>0.2229</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2022</v>
+        <v>0.2175</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.0054</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ QUILEZ</t>
+          <t>P. SUNOL CUBARSI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1215</v>
+        <v>0.337</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5402</v>
+        <v>0.2022</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4186</v>
+        <v>0.1348</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5526</v>
+        <v>0.1348</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5526</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.1348</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0614</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0614</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.614</v>
+        <v>0.1348</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.1348</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4788</v>
+        <v>0.2022</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4788</v>
+        <v>0.2022</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1016,291 +1046,311 @@
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>A. ABELLO GIRVES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.08069999999999999</v>
+        <v>0.2015</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5398</v>
+        <v>2.4008</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6205</v>
+        <v>-2.1993</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8982</v>
+        <v>-0.4417</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5337</v>
+        <v>0.5032</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3646</v>
+        <v>-0.9449</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8331</v>
+        <v>2.6392</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0167</v>
+        <v>2.2346</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8498</v>
+        <v>0.4047</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.7314</v>
+        <v>-3.081</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.517</v>
+        <v>-1.7314</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2144</v>
+        <v>-1.3496</v>
       </c>
       <c r="P8" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.5627</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-0.1953</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.7581</v>
-      </c>
       <c r="S8" t="n">
-        <v>0.6418</v>
+        <v>-0.0247</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1838</v>
+        <v>0.6564</v>
       </c>
       <c r="U8" t="n">
-        <v>0.458</v>
+        <v>-0.6811</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3869</v>
+        <v>0.2772</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7182</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1052</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>A. FERNANDEZ QUILEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6603</v>
+        <v>0.1215</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8273</v>
+        <v>0.5402</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4876</v>
+        <v>-0.4186</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2653</v>
+        <v>-0.5526</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6644</v>
+        <v>-0.5526</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9297</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0614</v>
+        <v>0.0614</v>
       </c>
       <c r="K9" t="n">
-        <v>2.0466</v>
+        <v>0.0614</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0148</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3267</v>
+        <v>-0.614</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3822</v>
+        <v>-0.614</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9445</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7581</v>
+        <v>0.1953</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1327</v>
+        <v>0.4788</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1769</v>
+        <v>0.4788</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3096</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8821</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7682</v>
+        <v>2.5398</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6503</v>
+        <v>-2.6205</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6819</v>
+        <v>-1.8982</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5733</v>
+        <v>-1.5337</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1086</v>
+        <v>-0.3646</v>
       </c>
       <c r="J10" t="n">
-        <v>2.3062</v>
+        <v>0.8331</v>
       </c>
       <c r="K10" t="n">
-        <v>1.6577</v>
+        <v>-0.0167</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6484</v>
+        <v>0.8498</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6243</v>
+        <v>-2.7314</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0844</v>
+        <v>-1.517</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5399</v>
+        <v>-1.2144</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-0.1953</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3687</v>
+        <v>0.6418</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1968</v>
+        <v>0.1838</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5655</v>
+        <v>0.458</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2186</v>
+        <v>-0.3869</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2186</v>
+        <v>1.7182</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4373</v>
+        <v>-2.1052</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1283</v>
+        <v>-0.6603</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.445</v>
+        <v>1.8273</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6833</v>
+        <v>-2.4876</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3757</v>
+        <v>-0.2653</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.8074</v>
+        <v>0.6644</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4317</v>
+        <v>-0.9297</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6532</v>
+        <v>2.0614</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.4902</v>
+        <v>2.0466</v>
       </c>
       <c r="L11" t="n">
-        <v>0.837</v>
+        <v>0.0148</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7225</v>
+        <v>-2.3267</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3172</v>
+        <v>-1.3822</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4052</v>
+        <v>-0.9445</v>
       </c>
       <c r="P11" t="n">
         <v>-1.7581</v>
@@ -1312,340 +1362,361 @@
         <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2717</v>
+        <v>-0.1327</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2207</v>
+        <v>0.1769</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.051</v>
+        <v>-0.3096</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2772</v>
+        <v>1.4959</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5545</v>
+        <v>2.7145</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8867</v>
+        <v>-0.8821</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8549</v>
+        <v>1.7682</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0319</v>
+        <v>-2.6503</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.153</v>
+        <v>1.6819</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.8074</v>
+        <v>1.5733</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.3456</v>
+        <v>0.1086</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.6259</v>
+        <v>2.3062</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.8995</v>
+        <v>1.6577</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7264</v>
+        <v>0.6484</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.5271</v>
+        <v>-0.6243</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9079</v>
+        <v>-0.0844</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6192</v>
+        <v>-0.5399</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3907</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1488</v>
+        <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3797</v>
+        <v>-0.3687</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.1968</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2629</v>
+        <v>-0.5655</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2772</v>
+        <v>-1.2186</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.4512</v>
+        <v>-4.8867</v>
       </c>
       <c r="E13" t="n">
-        <v>12.042</v>
+        <v>-3.8549</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.4931</v>
+        <v>-1.0319</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.4413</v>
+        <v>-5.153</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.164099999999999</v>
+        <v>-2.8074</v>
       </c>
       <c r="I13" t="n">
-        <v>4.722700000000001</v>
+        <v>-2.3456</v>
       </c>
       <c r="J13" t="n">
-        <v>15.6861</v>
+        <v>-2.6259</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5403</v>
+        <v>-1.8995</v>
       </c>
       <c r="L13" t="n">
-        <v>12.1456</v>
+        <v>-0.7264</v>
       </c>
       <c r="M13" t="n">
-        <v>-17.1275</v>
+        <v>-2.5271</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.704599999999999</v>
+        <v>-0.9079</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.423100000000001</v>
+        <v>-1.6192</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.9303</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.6507</v>
+        <v>-2.1488</v>
       </c>
       <c r="R13" t="n">
-        <v>11.7205</v>
+        <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4172</v>
+        <v>0.3797</v>
       </c>
       <c r="T13" t="n">
-        <v>3.0827</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.6655</v>
+        <v>-0.2629</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.4965999999999997</v>
+        <v>0.2772</v>
       </c>
       <c r="W13" t="n">
-        <v>7.9239</v>
+        <v>0.2772</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.4207</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB NAVÀS VISCOLA</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6093</v>
+        <v>-6.2562</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8981</v>
+        <v>-5.5729</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2888</v>
+        <v>-0.6833</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5497</v>
+        <v>-4.5036</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7552</v>
+        <v>-3.1144</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7945</v>
+        <v>-1.3893</v>
       </c>
       <c r="J14" t="n">
-        <v>6.0076</v>
+        <v>-2.7812</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4584</v>
+        <v>-1.7972</v>
       </c>
       <c r="L14" t="n">
-        <v>3.5491</v>
+        <v>-0.984</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4579</v>
+        <v>-1.7225</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7032</v>
+        <v>-1.3172</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7546</v>
+        <v>-0.4052</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1953</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9301</v>
+        <v>-3.1255</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7348</v>
+        <v>1.3674</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4093</v>
+        <v>-0.2717</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2113</v>
+        <v>-0.2207</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6206</v>
+        <v>-0.051</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6093</v>
+        <v>0.5545</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0549</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB NAVÀS VISCOLA</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5689</v>
+        <v>-3.451200000000002</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1285</v>
+        <v>12.042</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5596</v>
+        <v>-15.4931</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2273</v>
+        <v>-1.4413</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4983</v>
+        <v>-6.1641</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7256</v>
+        <v>4.722799999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6851</v>
+        <v>15.6859</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1996</v>
+        <v>3.5404</v>
       </c>
       <c r="L15" t="n">
-        <v>3.8847</v>
+        <v>12.1457</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.4579</v>
+        <v>-17.1275</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2988</v>
+        <v>-9.704599999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.1591</v>
+        <v>-7.4231</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3907</v>
+        <v>-2.9303</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9301</v>
+        <v>-14.6507</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5395</v>
+        <v>11.7205</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0178</v>
+        <v>1.4172</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4404</v>
+        <v>3.0827</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4225</v>
+        <v>-1.6655</v>
       </c>
       <c r="V15" t="n">
-        <v>2.7145</v>
+        <v>-0.4965999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>3.9331</v>
+        <v>7.9239</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2186</v>
-      </c>
+        <v>-8.420700000000002</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6829</v>
+        <v>3.6093</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9138</v>
+        <v>3.8981</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2309</v>
+        <v>-0.2888</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7216</v>
+        <v>3.5497</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2891</v>
+        <v>1.7552</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5675</v>
+        <v>1.7945</v>
       </c>
       <c r="J16" t="n">
-        <v>5.3094</v>
+        <v>6.0076</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8526</v>
+        <v>2.4584</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4568</v>
+        <v>3.5491</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.5878</v>
+        <v>-2.4579</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5636</v>
+        <v>-0.7032</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.0243</v>
+        <v>-1.7546</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9534</v>
+        <v>2.7348</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2153</v>
+        <v>-0.4093</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5346</v>
+        <v>0.2113</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3193</v>
+        <v>-0.6206</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2772</v>
+        <v>0.6642</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5456</v>
+        <v>3.2619</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7882</v>
+        <v>4.8215</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2425</v>
+        <v>-1.5596</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0098</v>
+        <v>0.9203</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7923</v>
+        <v>-0.8053</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7825</v>
+        <v>1.7256</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7592</v>
+        <v>3.3781</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2714</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5122</v>
+        <v>3.8847</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7494</v>
+        <v>-2.4579</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4792</v>
+        <v>-0.2988</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2702</v>
+        <v>-2.1591</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>2.5395</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1452</v>
+        <v>0.0178</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1424</v>
+        <v>0.4404</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0027</v>
+        <v>-0.4225</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6093</v>
+        <v>2.7145</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8865</v>
+        <v>3.9331</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3151</v>
+        <v>1.6829</v>
       </c>
       <c r="E18" t="n">
-        <v>4.6225</v>
+        <v>2.9138</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.3074</v>
+        <v>-1.2309</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2329</v>
+        <v>2.7216</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9322</v>
+        <v>3.2891</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6994</v>
+        <v>-0.5675</v>
       </c>
       <c r="J18" t="n">
-        <v>2.7606</v>
+        <v>5.3094</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7053</v>
+        <v>3.8526</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0553</v>
+        <v>1.4568</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5277</v>
+        <v>-2.5878</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7731</v>
+        <v>-0.5636</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7546</v>
+        <v>-2.0243</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5395</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5395</v>
+        <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2972</v>
+        <v>0.2153</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3661</v>
+        <v>0.5346</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6633</v>
+        <v>-0.3193</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.16</v>
+        <v>-0.2772</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.6559</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1977,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0861</v>
+        <v>1.5456</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7481</v>
+        <v>1.7882</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8342</v>
+        <v>-0.2425</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5406</v>
+        <v>0.0098</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3784</v>
+        <v>0.7923</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1623</v>
+        <v>-0.7825</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0974</v>
+        <v>0.7592</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.55</v>
+        <v>1.2714</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6475</v>
+        <v>-0.5122</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.638</v>
+        <v>-0.7494</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8283</v>
+        <v>-0.4792</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8097</v>
+        <v>-0.2702</v>
       </c>
       <c r="P19" t="n">
         <v>0.7814</v>
@@ -1936,28 +2022,33 @@
         <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2683</v>
+        <v>0.1452</v>
       </c>
       <c r="T19" t="n">
-        <v>0.432</v>
+        <v>0.1424</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7003</v>
+        <v>0.0027</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9414</v>
+        <v>0.6093</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>0.8865</v>
       </c>
       <c r="X19" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CASCALES FERNANDEZ</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4328</v>
+        <v>0.3151</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3061</v>
+        <v>4.6225</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1267</v>
+        <v>-4.3074</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5152</v>
+        <v>0.2329</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1011</v>
+        <v>1.9322</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.6163</v>
+        <v>-1.6994</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2263</v>
+        <v>2.7606</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0409</v>
+        <v>2.7053</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2673</v>
+        <v>0.0553</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2889</v>
+        <v>-2.5277</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0601</v>
+        <v>-0.7731</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.349</v>
+        <v>-1.7546</v>
       </c>
       <c r="P20" t="n">
-        <v>0.586</v>
+        <v>2.5395</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.586</v>
+        <v>2.5395</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1678</v>
+        <v>-0.2972</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.3661</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0881</v>
+        <v>-0.6633</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6642</v>
+        <v>-2.16</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6642</v>
+        <v>-3.6559</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4331</v>
+        <v>0.307</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.311</v>
+        <v>0.307</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1221</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0082</v>
+        <v>0.307</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1793</v>
+        <v>0.307</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1875</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2859</v>
+        <v>0.307</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1241</v>
+        <v>0.307</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1619</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2941</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0553</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3494</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2896</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1026</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.187</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. PLANELL IGLESIAS</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6446</v>
+        <v>-0.0861</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.989</v>
+        <v>1.7481</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6556</v>
+        <v>-1.8342</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2358</v>
+        <v>-1.5406</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-1.3784</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2274</v>
+        <v>-0.1623</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5514</v>
+        <v>0.0974</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0013</v>
+        <v>-0.55</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5527</v>
+        <v>0.6475</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6844</v>
+        <v>-1.638</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0097</v>
+        <v>-0.8283</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6747</v>
+        <v>-0.8097</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S22" t="n">
         <v>-0.2683</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4842</v>
+        <v>0.432</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2159</v>
+        <v>-0.7003</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.1638</v>
+        <v>0.9414</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1638</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. CASCALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,318 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4.125200000000001</v>
+        <v>-1.4328</v>
       </c>
       <c r="E23" t="n">
+        <v>-1.3061</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.1267</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2.5152</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1011</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-2.6163</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.2263</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-1.2673</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.2889</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.0601</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-1.349</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.1678</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.07969999999999999</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.0881</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A. FALL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-1.4331</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.311</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1.1221</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.0082</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1793</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.1875</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.1241</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.2941</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.0553</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.3494</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.2896</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.1026</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.7731</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A. PLANELL IGLESIAS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-3.6446</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.989</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.6556</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.2358</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.008399999999999999</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.2274</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.5514</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.5527</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.6844</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.6747</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.2683</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.4842</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.2159</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.1638</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.1638</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484362_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4.1252</v>
+      </c>
+      <c r="E26" t="n">
         <v>15.4931</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F26" t="n">
         <v>-11.3678</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G26" t="n">
         <v>1.4415</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H26" t="n">
         <v>6.1641</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I26" t="n">
         <v>-4.722799999999999</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J26" t="n">
         <v>17.1275</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K26" t="n">
         <v>9.7044</v>
       </c>
-      <c r="L23" t="n">
-        <v>7.423099999999999</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="L26" t="n">
+        <v>7.4231</v>
+      </c>
+      <c r="M26" t="n">
         <v>-15.6861</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N26" t="n">
         <v>-3.5405</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O26" t="n">
         <v>-12.1456</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P26" t="n">
         <v>2.9303</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q26" t="n">
         <v>-11.7204</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R26" t="n">
         <v>14.6508</v>
       </c>
-      <c r="S23" t="n">
-        <v>-0.743</v>
-      </c>
-      <c r="T23" t="n">
+      <c r="S26" t="n">
+        <v>-0.7430000000000001</v>
+      </c>
+      <c r="T26" t="n">
         <v>1.6655</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U26" t="n">
         <v>-2.4085</v>
       </c>
-      <c r="V23" t="n">
-        <v>0.4967000000000004</v>
-      </c>
-      <c r="W23" t="n">
+      <c r="V26" t="n">
+        <v>0.4967000000000001</v>
+      </c>
+      <c r="W26" t="n">
         <v>8.4206</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X26" t="n">
         <v>-7.9239</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
